--- a/HospedagemV1.xlsx
+++ b/HospedagemV1.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Arquivos Pessoais\Viagens\20250912 - Valencia_Lisboa\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{34F2293E-770F-4618-AFFC-228CBA01D883}" xr6:coauthVersionLast="46" xr6:coauthVersionMax="46" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7F6A91AA-C14E-4B7B-926B-E6449B56D2AC}" xr6:coauthVersionLast="46" xr6:coauthVersionMax="46" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" tabRatio="728" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" tabRatio="728" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Hospedagem" sheetId="3" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="371" uniqueCount="167">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="399" uniqueCount="183">
   <si>
     <t>Período</t>
   </si>
@@ -846,6 +846,56 @@
   </si>
   <si>
     <t>Livre escolha</t>
+  </si>
+  <si>
+    <t>Madrid -  Barcelona</t>
+  </si>
+  <si>
+    <t>Barcelona - Valencia</t>
+  </si>
+  <si>
+    <t>Trem: de Madrid para Barcelona</t>
+  </si>
+  <si>
+    <t>Trem: de Barcelona para Valencia</t>
+  </si>
+  <si>
+    <t>Cruzeiro Rio Sena (Barco)</t>
+  </si>
+  <si>
+    <t>Mont Saint Michel</t>
+  </si>
+  <si>
+    <t>Ilha Berlenga</t>
+  </si>
+  <si>
+    <t>Torre eiffel</t>
+  </si>
+  <si>
+    <t>Vencimento</t>
+  </si>
+  <si>
+    <t>Depositar para</t>
+  </si>
+  <si>
+    <t>Ana Claudia</t>
+  </si>
+  <si>
+    <t>PG</t>
+  </si>
+  <si>
+    <t>Sercotel Sorolla Palace</t>
+  </si>
+  <si>
+    <t xml:space="preserve">
+Sercotel Sorolla Palace
+Avenida de Las Cortes Valencianas, 58, Valência, 46015, Espanha</t>
+  </si>
+  <si>
+    <t>VISA 1611</t>
+  </si>
+  <si>
+    <t>Moderno, amplio y muy cómodo</t>
   </si>
 </sst>
 </file>
@@ -1154,7 +1204,7 @@
     <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="124">
+  <cellXfs count="129">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -1430,6 +1480,20 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1478,6 +1542,12 @@
     <xf numFmtId="44" fontId="0" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1489,15 +1559,6 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -1784,7 +1845,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:K15"/>
+  <dimension ref="A1:M15"/>
   <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="36" bestFit="1" customWidth="1"/>
@@ -1797,26 +1858,27 @@
     <col min="9" max="9" width="21.85546875" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="8.7109375" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="12.140625" style="18" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="13.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A1" s="102" t="s">
+    <row r="1" spans="1:13" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="A1" s="108" t="s">
         <v>113</v>
       </c>
-      <c r="B1" s="102"/>
-      <c r="C1" s="102"/>
-      <c r="D1" s="102"/>
-      <c r="E1" s="102"/>
-      <c r="F1" s="102"/>
-      <c r="G1" s="102"/>
-      <c r="H1" s="102"/>
-      <c r="I1" s="102"/>
-    </row>
-    <row r="2" spans="1:11" s="6" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="101" t="s">
+      <c r="B1" s="108"/>
+      <c r="C1" s="108"/>
+      <c r="D1" s="108"/>
+      <c r="E1" s="108"/>
+      <c r="F1" s="108"/>
+      <c r="G1" s="108"/>
+      <c r="H1" s="108"/>
+      <c r="I1" s="108"/>
+    </row>
+    <row r="2" spans="1:13" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="107" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="101"/>
+      <c r="B2" s="107"/>
       <c r="C2" s="5" t="s">
         <v>1</v>
       </c>
@@ -1845,7 +1907,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="3" spans="1:11" s="54" customFormat="1" ht="45" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:13" s="54" customFormat="1" ht="90" x14ac:dyDescent="0.25">
       <c r="A3" s="45">
         <v>45913</v>
       </c>
@@ -1856,10 +1918,10 @@
         <v>7</v>
       </c>
       <c r="D3" s="54" t="s">
-        <v>77</v>
+        <v>179</v>
       </c>
       <c r="E3" s="48">
-        <v>2934.38</v>
+        <v>2939.35</v>
       </c>
       <c r="F3" s="49">
         <v>488</v>
@@ -1869,16 +1931,23 @@
       </c>
       <c r="H3" s="48"/>
       <c r="I3" s="47" t="s">
-        <v>38</v>
+        <v>180</v>
       </c>
       <c r="J3" s="52" t="s">
         <v>18</v>
       </c>
       <c r="K3" s="53" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="4" spans="1:11" s="6" customFormat="1" ht="42.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>181</v>
+      </c>
+      <c r="L3" s="54" t="s">
+        <v>18</v>
+      </c>
+      <c r="M3" s="105">
+        <f>E6+E7+E11</f>
+        <v>7576.77</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13" s="6" customFormat="1" ht="42.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="7">
         <v>45915</v>
       </c>
@@ -1892,7 +1961,7 @@
         <v>9</v>
       </c>
       <c r="E4" s="9">
-        <v>5185</v>
+        <v>5451</v>
       </c>
       <c r="F4" s="12">
         <v>791.97</v>
@@ -1910,8 +1979,15 @@
       <c r="K4" s="17" t="s">
         <v>40</v>
       </c>
-    </row>
-    <row r="5" spans="1:11" s="54" customFormat="1" ht="75" x14ac:dyDescent="0.25">
+      <c r="L4" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="M4" s="106">
+        <f>E4+E6+E9+E10</f>
+        <v>12415</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13" s="54" customFormat="1" ht="75" x14ac:dyDescent="0.25">
       <c r="A5" s="45">
         <f t="shared" ref="A5:A11" si="0">B4</f>
         <v>45920</v>
@@ -1923,14 +1999,14 @@
         <v>7</v>
       </c>
       <c r="D5" s="47" t="s">
-        <v>78</v>
+        <v>182</v>
       </c>
       <c r="E5" s="48">
-        <v>1236</v>
+        <v>1297.31</v>
       </c>
       <c r="F5" s="49">
         <f>E5/6.6</f>
-        <v>187.27272727272728</v>
+        <v>196.56212121212121</v>
       </c>
       <c r="G5" s="50" t="s">
         <v>122</v>
@@ -1945,8 +2021,12 @@
       <c r="K5" s="53" t="s">
         <v>41</v>
       </c>
-    </row>
-    <row r="6" spans="1:11" s="6" customFormat="1" ht="45" x14ac:dyDescent="0.25">
+      <c r="M5" s="105">
+        <f>SUM(M3:M4)</f>
+        <v>19991.77</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13" s="6" customFormat="1" ht="45" x14ac:dyDescent="0.25">
       <c r="A6" s="7">
         <f t="shared" si="0"/>
         <v>45921</v>
@@ -1961,7 +2041,7 @@
         <v>11</v>
       </c>
       <c r="E6" s="9">
-        <v>2576</v>
+        <v>2749</v>
       </c>
       <c r="F6" s="12">
         <v>430.63</v>
@@ -1979,8 +2059,12 @@
       <c r="K6" s="17" t="s">
         <v>40</v>
       </c>
-    </row>
-    <row r="7" spans="1:11" s="54" customFormat="1" ht="45" x14ac:dyDescent="0.25">
+      <c r="M6" s="106">
+        <f>M5/6</f>
+        <v>3331.9616666666666</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13" s="54" customFormat="1" ht="45" x14ac:dyDescent="0.25">
       <c r="A7" s="90">
         <f t="shared" si="0"/>
         <v>45924</v>
@@ -2013,8 +2097,12 @@
       <c r="K7" s="98" t="s">
         <v>41</v>
       </c>
-    </row>
-    <row r="8" spans="1:11" s="54" customFormat="1" ht="45" x14ac:dyDescent="0.25">
+      <c r="M7" s="105">
+        <f>M6*2</f>
+        <v>6663.9233333333332</v>
+      </c>
+    </row>
+    <row r="8" spans="1:13" s="54" customFormat="1" ht="45" x14ac:dyDescent="0.25">
       <c r="A8" s="90">
         <f t="shared" si="0"/>
         <v>45926</v>
@@ -2048,7 +2136,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="9" spans="1:11" s="6" customFormat="1" ht="45" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:13" s="6" customFormat="1" ht="45" x14ac:dyDescent="0.25">
       <c r="A9" s="7">
         <f t="shared" si="0"/>
         <v>45928</v>
@@ -2082,7 +2170,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="10" spans="1:11" s="6" customFormat="1" ht="45" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:13" s="6" customFormat="1" ht="45" x14ac:dyDescent="0.25">
       <c r="A10" s="7">
         <f t="shared" si="0"/>
         <v>45931</v>
@@ -2116,7 +2204,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="11" spans="1:11" s="54" customFormat="1" ht="60" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:13" s="54" customFormat="1" ht="60" x14ac:dyDescent="0.25">
       <c r="A11" s="45">
         <f t="shared" si="0"/>
         <v>45932</v>
@@ -2151,21 +2239,21 @@
         <v>41</v>
       </c>
     </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:13" x14ac:dyDescent="0.25">
       <c r="E12" s="41">
         <f>SUM(E3:E11)</f>
-        <v>22657.81</v>
+        <v>23163.09</v>
       </c>
       <c r="F12" s="42" t="e">
         <f>SUM(F3:F11)</f>
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:13" x14ac:dyDescent="0.25">
       <c r="C14" s="31"/>
       <c r="E14" s="21"/>
     </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:13" x14ac:dyDescent="0.25">
       <c r="E15" s="21"/>
     </row>
   </sheetData>
@@ -2220,16 +2308,16 @@
       </c>
       <c r="B2" s="26"/>
       <c r="C2" s="26"/>
-      <c r="D2" s="103" t="s">
+      <c r="D2" s="109" t="s">
         <v>66</v>
       </c>
-      <c r="E2" s="103"/>
-      <c r="F2" s="103"/>
-      <c r="G2" s="103"/>
-      <c r="H2" s="103"/>
-      <c r="I2" s="103"/>
-      <c r="J2" s="103"/>
-      <c r="K2" s="103"/>
+      <c r="E2" s="109"/>
+      <c r="F2" s="109"/>
+      <c r="G2" s="109"/>
+      <c r="H2" s="109"/>
+      <c r="I2" s="109"/>
+      <c r="J2" s="109"/>
+      <c r="K2" s="109"/>
     </row>
     <row r="3" spans="1:11" s="18" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A3" s="5" t="s">
@@ -2267,10 +2355,10 @@
       </c>
     </row>
     <row r="4" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A4" s="104" t="s">
+      <c r="A4" s="110" t="s">
         <v>56</v>
       </c>
-      <c r="B4" s="105" t="s">
+      <c r="B4" s="111" t="s">
         <v>92</v>
       </c>
       <c r="C4" s="32"/>
@@ -2300,8 +2388,8 @@
       </c>
     </row>
     <row r="5" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A5" s="104"/>
-      <c r="B5" s="106"/>
+      <c r="A5" s="110"/>
+      <c r="B5" s="112"/>
       <c r="C5" s="33"/>
       <c r="D5" s="7" t="s">
         <v>58</v>
@@ -2329,8 +2417,8 @@
       </c>
     </row>
     <row r="6" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A6" s="104"/>
-      <c r="B6" s="106"/>
+      <c r="A6" s="110"/>
+      <c r="B6" s="112"/>
       <c r="C6" s="33"/>
       <c r="D6" s="7" t="s">
         <v>59</v>
@@ -2358,10 +2446,10 @@
       </c>
     </row>
     <row r="7" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A7" s="104" t="s">
+      <c r="A7" s="110" t="s">
         <v>19</v>
       </c>
-      <c r="B7" s="106"/>
+      <c r="B7" s="112"/>
       <c r="C7" s="33"/>
       <c r="D7" s="7" t="s">
         <v>57</v>
@@ -2389,8 +2477,8 @@
       </c>
     </row>
     <row r="8" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A8" s="104"/>
-      <c r="B8" s="106"/>
+      <c r="A8" s="110"/>
+      <c r="B8" s="112"/>
       <c r="C8" s="33"/>
       <c r="D8" s="7" t="s">
         <v>58</v>
@@ -2418,8 +2506,8 @@
       </c>
     </row>
     <row r="9" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A9" s="104"/>
-      <c r="B9" s="106"/>
+      <c r="A9" s="110"/>
+      <c r="B9" s="112"/>
       <c r="C9" s="33"/>
       <c r="D9" s="7" t="s">
         <v>59</v>
@@ -2447,10 +2535,10 @@
       </c>
     </row>
     <row r="10" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A10" s="104" t="s">
+      <c r="A10" s="110" t="s">
         <v>63</v>
       </c>
-      <c r="B10" s="106"/>
+      <c r="B10" s="112"/>
       <c r="C10" s="33"/>
       <c r="D10" s="7" t="s">
         <v>57</v>
@@ -2478,8 +2566,8 @@
       </c>
     </row>
     <row r="11" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A11" s="104"/>
-      <c r="B11" s="106"/>
+      <c r="A11" s="110"/>
+      <c r="B11" s="112"/>
       <c r="C11" s="33"/>
       <c r="D11" s="7" t="s">
         <v>58</v>
@@ -2507,8 +2595,8 @@
       </c>
     </row>
     <row r="12" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A12" s="104"/>
-      <c r="B12" s="106"/>
+      <c r="A12" s="110"/>
+      <c r="B12" s="112"/>
       <c r="C12" s="33"/>
       <c r="D12" s="7" t="s">
         <v>59</v>
@@ -2536,10 +2624,10 @@
       </c>
     </row>
     <row r="13" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A13" s="104" t="s">
+      <c r="A13" s="110" t="s">
         <v>64</v>
       </c>
-      <c r="B13" s="106"/>
+      <c r="B13" s="112"/>
       <c r="C13" s="33"/>
       <c r="D13" s="7" t="s">
         <v>57</v>
@@ -2567,8 +2655,8 @@
       </c>
     </row>
     <row r="14" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A14" s="104"/>
-      <c r="B14" s="106"/>
+      <c r="A14" s="110"/>
+      <c r="B14" s="112"/>
       <c r="C14" s="33"/>
       <c r="D14" s="7" t="s">
         <v>58</v>
@@ -2596,8 +2684,8 @@
       </c>
     </row>
     <row r="15" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A15" s="104"/>
-      <c r="B15" s="107"/>
+      <c r="A15" s="110"/>
+      <c r="B15" s="113"/>
       <c r="C15" s="34"/>
       <c r="D15" s="7" t="s">
         <v>59</v>
@@ -2628,24 +2716,24 @@
       <c r="A17" s="26" t="s">
         <v>65</v>
       </c>
-      <c r="B17" s="108" t="s">
+      <c r="B17" s="114" t="s">
         <v>67</v>
       </c>
-      <c r="C17" s="109"/>
-      <c r="D17" s="109"/>
-      <c r="E17" s="109"/>
-      <c r="F17" s="109"/>
-      <c r="G17" s="109"/>
-      <c r="H17" s="109"/>
-      <c r="I17" s="109"/>
-      <c r="J17" s="109"/>
-      <c r="K17" s="110"/>
+      <c r="C17" s="115"/>
+      <c r="D17" s="115"/>
+      <c r="E17" s="115"/>
+      <c r="F17" s="115"/>
+      <c r="G17" s="115"/>
+      <c r="H17" s="115"/>
+      <c r="I17" s="115"/>
+      <c r="J17" s="115"/>
+      <c r="K17" s="116"/>
     </row>
     <row r="18" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A18" s="104" t="s">
+      <c r="A18" s="110" t="s">
         <v>68</v>
       </c>
-      <c r="B18" s="104" t="s">
+      <c r="B18" s="110" t="s">
         <v>93</v>
       </c>
       <c r="C18" s="36" t="s">
@@ -2666,21 +2754,21 @@
       <c r="H18" s="25" t="s">
         <v>62</v>
       </c>
-      <c r="I18" s="111">
+      <c r="I18" s="117">
         <v>1231.8800000000001</v>
       </c>
-      <c r="J18" s="113">
+      <c r="J18" s="119">
         <f>(I18*6.237)+(I18*6.237)*1.1%</f>
         <v>7767.7511511600014</v>
       </c>
-      <c r="K18" s="115">
+      <c r="K18" s="121">
         <f>J18/6</f>
         <v>1294.6251918600003</v>
       </c>
     </row>
     <row r="19" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A19" s="104"/>
-      <c r="B19" s="104"/>
+      <c r="A19" s="110"/>
+      <c r="B19" s="110"/>
       <c r="C19" s="36" t="s">
         <v>105</v>
       </c>
@@ -2699,9 +2787,9 @@
       <c r="H19" s="25" t="s">
         <v>62</v>
       </c>
-      <c r="I19" s="112"/>
-      <c r="J19" s="114"/>
-      <c r="K19" s="116"/>
+      <c r="I19" s="118"/>
+      <c r="J19" s="120"/>
+      <c r="K19" s="122"/>
     </row>
     <row r="20" spans="1:12" x14ac:dyDescent="0.25">
       <c r="K20" s="28"/>
@@ -2712,16 +2800,16 @@
       </c>
       <c r="B21" s="26"/>
       <c r="C21" s="26"/>
-      <c r="D21" s="103" t="s">
+      <c r="D21" s="109" t="s">
         <v>80</v>
       </c>
-      <c r="E21" s="103"/>
-      <c r="F21" s="103"/>
-      <c r="G21" s="103"/>
-      <c r="H21" s="103"/>
-      <c r="I21" s="103"/>
-      <c r="J21" s="103"/>
-      <c r="K21" s="103"/>
+      <c r="E21" s="109"/>
+      <c r="F21" s="109"/>
+      <c r="G21" s="109"/>
+      <c r="H21" s="109"/>
+      <c r="I21" s="109"/>
+      <c r="J21" s="109"/>
+      <c r="K21" s="109"/>
     </row>
     <row r="22" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A22" s="17" t="s">
@@ -3051,7 +3139,7 @@
       <c r="D12" s="62"/>
       <c r="E12" s="70"/>
     </row>
-    <row r="13" spans="1:5" ht="112.5" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:5" ht="93.75" x14ac:dyDescent="0.25">
       <c r="A13" s="67">
         <f t="shared" si="0"/>
         <v>45923</v>
@@ -3073,7 +3161,7 @@
       <c r="B14" s="72" t="s">
         <v>151</v>
       </c>
-      <c r="C14" s="122" t="s">
+      <c r="C14" s="123" t="s">
         <v>129</v>
       </c>
       <c r="D14" s="73"/>
@@ -3087,7 +3175,7 @@
       <c r="B15" s="72" t="s">
         <v>166</v>
       </c>
-      <c r="C15" s="123"/>
+      <c r="C15" s="124"/>
       <c r="D15" s="73"/>
       <c r="E15" s="62"/>
     </row>
@@ -3102,7 +3190,7 @@
       <c r="C16" s="99" t="s">
         <v>153</v>
       </c>
-      <c r="D16" s="121"/>
+      <c r="D16" s="101"/>
       <c r="E16" s="62"/>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.25">
@@ -3119,7 +3207,7 @@
       <c r="D17" s="62"/>
       <c r="E17" s="62"/>
     </row>
-    <row r="18" spans="1:5" ht="75" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:5" ht="56.25" x14ac:dyDescent="0.25">
       <c r="A18" s="63">
         <f t="shared" si="0"/>
         <v>45928</v>
@@ -3419,17 +3507,17 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1" s="117" t="s">
+      <c r="A1" s="125" t="s">
         <v>94</v>
       </c>
-      <c r="B1" s="117"/>
-      <c r="C1" s="117"/>
-      <c r="D1" s="117"/>
-      <c r="E1" s="117"/>
-      <c r="F1" s="117"/>
-      <c r="G1" s="117"/>
-      <c r="H1" s="117"/>
-      <c r="I1" s="117"/>
+      <c r="B1" s="125"/>
+      <c r="C1" s="125"/>
+      <c r="D1" s="125"/>
+      <c r="E1" s="125"/>
+      <c r="F1" s="125"/>
+      <c r="G1" s="125"/>
+      <c r="H1" s="125"/>
+      <c r="I1" s="125"/>
       <c r="J1" s="23" t="s">
         <v>72</v>
       </c>
@@ -3442,17 +3530,17 @@
         <v>65</v>
       </c>
       <c r="B2" s="26"/>
-      <c r="C2" s="103" t="s">
+      <c r="C2" s="109" t="s">
         <v>114</v>
       </c>
-      <c r="D2" s="103"/>
-      <c r="E2" s="103"/>
-      <c r="F2" s="103"/>
-      <c r="G2" s="103"/>
-      <c r="H2" s="103"/>
-      <c r="I2" s="103"/>
-      <c r="J2" s="103"/>
-      <c r="K2" s="103"/>
+      <c r="D2" s="109"/>
+      <c r="E2" s="109"/>
+      <c r="F2" s="109"/>
+      <c r="G2" s="109"/>
+      <c r="H2" s="109"/>
+      <c r="I2" s="109"/>
+      <c r="J2" s="109"/>
+      <c r="K2" s="109"/>
     </row>
     <row r="3" spans="1:12" s="18" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A3" s="5" t="s">
@@ -3488,10 +3576,10 @@
       </c>
     </row>
     <row r="4" spans="1:12" ht="27" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="104" t="s">
+      <c r="A4" s="110" t="s">
         <v>68</v>
       </c>
-      <c r="B4" s="105" t="s">
+      <c r="B4" s="111" t="s">
         <v>95</v>
       </c>
       <c r="C4" s="7" t="s">
@@ -3503,7 +3591,7 @@
       <c r="E4" s="22" t="s">
         <v>102</v>
       </c>
-      <c r="F4" s="118" t="s">
+      <c r="F4" s="126" t="s">
         <v>103</v>
       </c>
       <c r="G4" s="15">
@@ -3525,8 +3613,8 @@
       </c>
     </row>
     <row r="5" spans="1:12" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="104"/>
-      <c r="B5" s="107"/>
+      <c r="A5" s="110"/>
+      <c r="B5" s="113"/>
       <c r="C5" s="7" t="s">
         <v>69</v>
       </c>
@@ -3536,7 +3624,7 @@
       <c r="E5" s="22" t="s">
         <v>101</v>
       </c>
-      <c r="F5" s="119"/>
+      <c r="F5" s="127"/>
       <c r="G5" s="15">
         <v>0.5625</v>
       </c>
@@ -3557,19 +3645,19 @@
       <c r="K6" s="28"/>
     </row>
     <row r="9" spans="1:12" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A9" s="102" t="s">
+      <c r="A9" s="108" t="s">
         <v>130</v>
       </c>
-      <c r="B9" s="102"/>
-      <c r="C9" s="102"/>
-      <c r="D9" s="102"/>
-      <c r="E9" s="102"/>
-      <c r="F9" s="102"/>
-      <c r="G9" s="102"/>
-      <c r="H9" s="102"/>
-      <c r="I9" s="102"/>
-      <c r="J9" s="102"/>
-      <c r="K9" s="102"/>
+      <c r="B9" s="108"/>
+      <c r="C9" s="108"/>
+      <c r="D9" s="108"/>
+      <c r="E9" s="108"/>
+      <c r="F9" s="108"/>
+      <c r="G9" s="108"/>
+      <c r="H9" s="108"/>
+      <c r="I9" s="108"/>
+      <c r="J9" s="108"/>
+      <c r="K9" s="108"/>
     </row>
     <row r="10" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
@@ -3821,10 +3909,10 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:11" s="6" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="101" t="s">
+      <c r="A1" s="107" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="101"/>
+      <c r="B1" s="107"/>
       <c r="C1" s="5" t="s">
         <v>1</v>
       </c>
@@ -4185,12 +4273,12 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
-  <dimension ref="A1:H12"/>
+  <dimension ref="A1:H29"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="34" customWidth="1"/>
-    <col min="2" max="2" width="10.5703125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="10.85546875" customWidth="1"/>
+    <col min="1" max="1" width="41.85546875" customWidth="1"/>
+    <col min="2" max="2" width="12.140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="13.28515625" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="13" customWidth="1"/>
     <col min="5" max="5" width="12.28515625" customWidth="1"/>
     <col min="6" max="7" width="12.140625" bestFit="1" customWidth="1"/>
@@ -4198,16 +4286,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A1" s="120" t="s">
+      <c r="A1" s="128" t="s">
         <v>145</v>
       </c>
-      <c r="B1" s="120"/>
-      <c r="C1" s="120"/>
-      <c r="D1" s="120"/>
-      <c r="E1" s="120"/>
-      <c r="F1" s="120"/>
-      <c r="G1" s="120"/>
-      <c r="H1" s="120"/>
+      <c r="B1" s="128"/>
+      <c r="C1" s="128"/>
+      <c r="D1" s="128"/>
+      <c r="E1" s="128"/>
+      <c r="F1" s="128"/>
+      <c r="G1" s="128"/>
+      <c r="H1" s="128"/>
     </row>
     <row r="2" spans="1:8" s="18" customFormat="1" ht="45" x14ac:dyDescent="0.25">
       <c r="A2" s="85" t="s">
@@ -4362,7 +4450,7 @@
       </c>
       <c r="H6" s="39"/>
     </row>
-    <row r="7" spans="1:8" ht="30" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A7" s="84" t="str">
         <f>'Transfer  Voucher'!B14</f>
         <v>Paris: Torre Eiffel 2º andar (4 pessoas)</v>
@@ -4394,16 +4482,16 @@
       <c r="H7" s="39"/>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A8" s="120" t="s">
+      <c r="A8" s="128" t="s">
         <v>144</v>
       </c>
-      <c r="B8" s="120"/>
-      <c r="C8" s="120"/>
-      <c r="D8" s="120"/>
-      <c r="E8" s="120"/>
-      <c r="F8" s="120"/>
-      <c r="G8" s="120"/>
-      <c r="H8" s="120"/>
+      <c r="B8" s="128"/>
+      <c r="C8" s="128"/>
+      <c r="D8" s="128"/>
+      <c r="E8" s="128"/>
+      <c r="F8" s="128"/>
+      <c r="G8" s="128"/>
+      <c r="H8" s="128"/>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A9" s="80" t="str">
@@ -4437,32 +4525,207 @@
       <c r="H9" s="36"/>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="E10" s="80" t="s">
+      <c r="A10" s="102" t="s">
+        <v>167</v>
+      </c>
+      <c r="C10" s="103"/>
+      <c r="D10" s="21"/>
+      <c r="E10" s="82">
+        <f>F10/4</f>
+        <v>129</v>
+      </c>
+      <c r="F10" s="82">
+        <f>510+6</f>
+        <v>516</v>
+      </c>
+      <c r="G10" s="21"/>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A11" s="102" t="s">
+        <v>168</v>
+      </c>
+      <c r="C11" s="103"/>
+      <c r="D11" s="21"/>
+      <c r="E11" s="82">
+        <f>F11/4</f>
+        <v>375.5575</v>
+      </c>
+      <c r="F11" s="82">
+        <f>1487.23+15</f>
+        <v>1502.23</v>
+      </c>
+      <c r="G11" s="21"/>
+    </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="E12" s="80" t="s">
         <v>150</v>
       </c>
-      <c r="F10" s="82">
+      <c r="F12" s="82">
         <f>SUM(F3:F7,F9)</f>
         <v>5934.374175847619</v>
       </c>
-      <c r="G10" s="21"/>
-    </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="E11" s="80" t="s">
+      <c r="G12" s="21"/>
+    </row>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="E13" s="80" t="s">
         <v>147</v>
       </c>
-      <c r="F11" s="89">
+      <c r="F13" s="89">
         <f>SUM(H3:H7,H9)</f>
         <v>702.10799999999995</v>
       </c>
     </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="E12" s="80" t="s">
+    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="E14" s="80" t="s">
         <v>149</v>
       </c>
-      <c r="F12" s="82">
-        <f>F10-F11</f>
+      <c r="F14" s="82">
+        <f>F12-F13</f>
         <v>5232.2661758476188</v>
       </c>
+    </row>
+    <row r="18" spans="1:5" ht="30" x14ac:dyDescent="0.25">
+      <c r="A18" s="85" t="s">
+        <v>138</v>
+      </c>
+      <c r="B18" s="86" t="s">
+        <v>18</v>
+      </c>
+      <c r="C18" s="86" t="s">
+        <v>175</v>
+      </c>
+      <c r="D18" s="87" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A19" s="84" t="s">
+        <v>169</v>
+      </c>
+      <c r="B19" s="82">
+        <f>510+6</f>
+        <v>516</v>
+      </c>
+      <c r="C19" s="104">
+        <v>45848</v>
+      </c>
+      <c r="D19" s="39" t="s">
+        <v>177</v>
+      </c>
+      <c r="E19" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A20" s="84" t="s">
+        <v>170</v>
+      </c>
+      <c r="B20" s="9">
+        <f>1487.23+15</f>
+        <v>1502.23</v>
+      </c>
+      <c r="C20" s="104">
+        <v>45848</v>
+      </c>
+      <c r="D20" s="39" t="s">
+        <v>177</v>
+      </c>
+      <c r="E20" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A21" s="84" t="s">
+        <v>171</v>
+      </c>
+      <c r="B21" s="9">
+        <v>460</v>
+      </c>
+      <c r="C21" s="104">
+        <v>45848</v>
+      </c>
+      <c r="D21" s="39" t="s">
+        <v>177</v>
+      </c>
+      <c r="E21" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A22" s="84" t="s">
+        <v>174</v>
+      </c>
+      <c r="B22" s="9">
+        <v>1778</v>
+      </c>
+      <c r="C22" s="104">
+        <v>45848</v>
+      </c>
+      <c r="D22" s="39" t="s">
+        <v>177</v>
+      </c>
+      <c r="E22" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A23" s="84" t="s">
+        <v>172</v>
+      </c>
+      <c r="B23" s="9">
+        <v>886.5</v>
+      </c>
+      <c r="C23" s="104">
+        <v>45848</v>
+      </c>
+      <c r="D23" s="39" t="s">
+        <v>177</v>
+      </c>
+      <c r="E23" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A24" s="80" t="s">
+        <v>173</v>
+      </c>
+      <c r="B24" s="82">
+        <f>(1443.21/6)*4</f>
+        <v>962.14</v>
+      </c>
+      <c r="C24" s="104">
+        <v>45870</v>
+      </c>
+      <c r="D24" s="39" t="s">
+        <v>19</v>
+      </c>
+      <c r="E24" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A25" s="102" t="s">
+        <v>167</v>
+      </c>
+      <c r="B25" s="82"/>
+      <c r="C25" s="21"/>
+    </row>
+    <row r="26" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A26" s="102" t="s">
+        <v>168</v>
+      </c>
+      <c r="B26" s="82"/>
+      <c r="C26" s="21"/>
+    </row>
+    <row r="27" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B27" s="82"/>
+      <c r="C27" s="21"/>
+    </row>
+    <row r="28" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B28" s="89"/>
+    </row>
+    <row r="29" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B29" s="82"/>
     </row>
   </sheetData>
   <mergeCells count="2">
